--- a/Data/Questionnaires/Questionnaires_SLAM_B.xlsx
+++ b/Data/Questionnaires/Questionnaires_SLAM_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\Questionnaires\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E828BC9C-3C11-4642-9289-4B77D7B99608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085C1FFE-E10A-489C-97DB-E3EB282F0FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="799">
   <si>
     <t>NOM</t>
   </si>
@@ -1690,9 +1690,6 @@
   </si>
   <si>
     <t>NON_(OUVERTURE)</t>
-  </si>
-  <si>
-    <t>Lisc</t>
   </si>
   <si>
     <t>AGENT FORESTIER</t>
@@ -3308,7 +3305,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:CV78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3625,7 +3621,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>100</v>
       </c>
@@ -3803,7 +3799,7 @@
       <c r="CU2" s="2"/>
       <c r="CV2" s="2"/>
     </row>
-    <row r="3" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>137</v>
       </c>
@@ -3967,7 +3963,7 @@
       <c r="CU3" s="2"/>
       <c r="CV3" s="2"/>
     </row>
-    <row r="4" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>160</v>
       </c>
@@ -4169,7 +4165,7 @@
         <v>189</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>190</v>
@@ -4265,7 +4261,7 @@
       <c r="CU5" s="2"/>
       <c r="CV5" s="2"/>
     </row>
-    <row r="6" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>191</v>
       </c>
@@ -4447,7 +4443,7 @@
       <c r="CU6" s="2"/>
       <c r="CV6" s="2"/>
     </row>
-    <row r="7" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>210</v>
       </c>
@@ -4625,7 +4621,7 @@
       <c r="CU7" s="2"/>
       <c r="CV7" s="2"/>
     </row>
-    <row r="8" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>191</v>
       </c>
@@ -4831,7 +4827,7 @@
         <v>189</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>190</v>
@@ -4927,7 +4923,7 @@
       <c r="CU9" s="2"/>
       <c r="CV9" s="2"/>
     </row>
-    <row r="10" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>243</v>
       </c>
@@ -5107,7 +5103,7 @@
       <c r="CU10" s="2"/>
       <c r="CV10" s="2"/>
     </row>
-    <row r="11" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>260</v>
       </c>
@@ -5237,7 +5233,7 @@
       <c r="CU11" s="2"/>
       <c r="CV11" s="2"/>
     </row>
-    <row r="12" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>265</v>
       </c>
@@ -5393,7 +5389,7 @@
         <v>189</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>190</v>
@@ -5489,7 +5485,7 @@
       <c r="CU13" s="2"/>
       <c r="CV13" s="2"/>
     </row>
-    <row r="14" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>280</v>
       </c>
@@ -5673,7 +5669,7 @@
       <c r="CU14" s="2"/>
       <c r="CV14" s="2"/>
     </row>
-    <row r="15" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>301</v>
       </c>
@@ -5881,7 +5877,7 @@
         <v>189</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>190</v>
@@ -5977,7 +5973,7 @@
       <c r="CU16" s="2"/>
       <c r="CV16" s="2"/>
     </row>
-    <row r="17" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>326</v>
       </c>
@@ -6151,7 +6147,7 @@
       <c r="CU17" s="2"/>
       <c r="CV17" s="2"/>
     </row>
-    <row r="18" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>137</v>
       </c>
@@ -6325,7 +6321,7 @@
       <c r="CU18" s="2"/>
       <c r="CV18" s="2"/>
     </row>
-    <row r="19" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>137</v>
       </c>
@@ -6501,7 +6497,7 @@
       <c r="CU19" s="2"/>
       <c r="CV19" s="2"/>
     </row>
-    <row r="20" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>160</v>
       </c>
@@ -6681,7 +6677,7 @@
       <c r="CU20" s="2"/>
       <c r="CV20" s="2"/>
     </row>
-    <row r="21" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>160</v>
       </c>
@@ -6863,7 +6859,7 @@
       <c r="CU21" s="2"/>
       <c r="CV21" s="2"/>
     </row>
-    <row r="22" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>160</v>
       </c>
@@ -7035,7 +7031,7 @@
       <c r="CU22" s="2"/>
       <c r="CV22" s="2"/>
     </row>
-    <row r="23" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>378</v>
       </c>
@@ -7207,7 +7203,7 @@
       <c r="CU23" s="2"/>
       <c r="CV23" s="2"/>
     </row>
-    <row r="24" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>137</v>
       </c>
@@ -7383,7 +7379,7 @@
       <c r="CU24" s="2"/>
       <c r="CV24" s="2"/>
     </row>
-    <row r="25" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>137</v>
       </c>
@@ -7567,7 +7563,7 @@
       <c r="CU25" s="2"/>
       <c r="CV25" s="2"/>
     </row>
-    <row r="26" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>137</v>
       </c>
@@ -7759,7 +7755,7 @@
       <c r="CU26" s="2"/>
       <c r="CV26" s="2"/>
     </row>
-    <row r="27" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>137</v>
       </c>
@@ -7977,7 +7973,7 @@
         <v>189</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>190</v>
@@ -8073,7 +8069,7 @@
       <c r="CU28" s="2"/>
       <c r="CV28" s="2"/>
     </row>
-    <row r="29" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>426</v>
       </c>
@@ -8249,7 +8245,7 @@
       <c r="CU29" s="2"/>
       <c r="CV29" s="2"/>
     </row>
-    <row r="30" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>137</v>
       </c>
@@ -8427,7 +8423,7 @@
       <c r="CU30" s="2"/>
       <c r="CV30" s="2"/>
     </row>
-    <row r="31" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>421</v>
       </c>
@@ -8601,7 +8597,7 @@
       <c r="CU31" s="2"/>
       <c r="CV31" s="2"/>
     </row>
-    <row r="32" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>454</v>
       </c>
@@ -8771,7 +8767,7 @@
       <c r="CU32" s="2"/>
       <c r="CV32" s="2"/>
     </row>
-    <row r="33" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>465</v>
       </c>
@@ -8985,7 +8981,7 @@
         <v>189</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>190</v>
@@ -9081,7 +9077,7 @@
       <c r="CU34" s="2"/>
       <c r="CV34" s="2"/>
     </row>
-    <row r="35" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>484</v>
       </c>
@@ -9259,7 +9255,7 @@
       <c r="CU35" s="2"/>
       <c r="CV35" s="2"/>
     </row>
-    <row r="36" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>498</v>
       </c>
@@ -9387,7 +9383,7 @@
       <c r="CU36" s="2"/>
       <c r="CV36" s="2"/>
     </row>
-    <row r="37" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>137</v>
       </c>
@@ -9561,7 +9557,7 @@
       <c r="CU37" s="2"/>
       <c r="CV37" s="2"/>
     </row>
-    <row r="38" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>210</v>
       </c>
@@ -9747,7 +9743,7 @@
       <c r="CU38" s="2"/>
       <c r="CV38" s="2"/>
     </row>
-    <row r="39" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>183</v>
       </c>
@@ -9758,7 +9754,7 @@
         <v>185</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>554</v>
+        <v>186</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>104</v>
@@ -9770,10 +9766,10 @@
         <v>188</v>
       </c>
       <c r="H39" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -9834,10 +9830,10 @@
       </c>
       <c r="BM39" s="2"/>
       <c r="BN39" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="BO39" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="BO39" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="BP39" s="2">
         <v>0</v>
@@ -9847,78 +9843,78 @@
       </c>
       <c r="BR39" s="2"/>
       <c r="BS39" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="BT39" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="BT39" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="BU39" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV39" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="BW39" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="BW39" s="2" t="s">
+      <c r="BX39" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="BX39" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="BY39" s="2" t="s">
         <v>537</v>
       </c>
       <c r="BZ39" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="CA39" s="2" t="s">
         <v>185</v>
       </c>
       <c r="CB39" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="CC39" s="2"/>
       <c r="CD39" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="CE39" s="2"/>
       <c r="CF39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CG39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CH39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CI39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CJ39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CK39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CL39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CM39" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="CN39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CO39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CP39" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="CQ39" s="2" t="s">
         <v>550</v>
       </c>
       <c r="CR39" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="CS39" s="2" t="s">
         <v>173</v>
@@ -9929,7 +9925,7 @@
       <c r="CU39" s="2"/>
       <c r="CV39" s="2"/>
     </row>
-    <row r="40" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>243</v>
       </c>
@@ -9952,10 +9948,10 @@
         <v>247</v>
       </c>
       <c r="H40" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -10016,10 +10012,10 @@
       </c>
       <c r="BM40" s="2"/>
       <c r="BN40" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="BO40" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BP40" s="2">
         <v>1</v>
@@ -10029,22 +10025,22 @@
       </c>
       <c r="BR40" s="2"/>
       <c r="BS40" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="BT40" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="BT40" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="BU40" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV40" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BW40" s="2" t="s">
         <v>450</v>
       </c>
       <c r="BX40" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="BY40" s="2" t="s">
         <v>514</v>
@@ -10052,56 +10048,56 @@
       <c r="BZ40" s="2"/>
       <c r="CA40" s="2"/>
       <c r="CB40" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="CC40" s="2"/>
       <c r="CD40" s="2" t="s">
         <v>82</v>
       </c>
       <c r="CE40" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="CF40" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="CF40" s="2" t="s">
+      <c r="CG40" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="CG40" s="2" t="s">
+      <c r="CH40" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="CH40" s="2" t="s">
+      <c r="CI40" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="CI40" s="2" t="s">
+      <c r="CJ40" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="CJ40" s="2" t="s">
+      <c r="CK40" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="CL40" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="CK40" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="CL40" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="CM40" s="2" t="s">
         <v>524</v>
       </c>
       <c r="CN40" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="CO40" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="CO40" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="CP40" s="2" t="s">
         <v>450</v>
       </c>
       <c r="CQ40" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="CR40" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="CR40" s="2" t="s">
+      <c r="CS40" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="CS40" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="CT40" s="2" t="s">
         <v>553</v>
@@ -10109,7 +10105,7 @@
       <c r="CU40" s="2"/>
       <c r="CV40" s="2"/>
     </row>
-    <row r="41" spans="1:100" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:100" ht="58" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>265</v>
       </c>
@@ -10132,10 +10128,10 @@
         <v>270</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -10196,10 +10192,10 @@
       </c>
       <c r="BM41" s="2"/>
       <c r="BN41" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="BO41" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="BO41" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="BP41" s="2" t="s">
         <v>173</v>
@@ -10208,23 +10204,23 @@
         <v>506</v>
       </c>
       <c r="BR41" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="BS41" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="BS41" s="2" t="s">
+      <c r="BT41" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="BT41" s="2" t="s">
+      <c r="BU41" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="BU41" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="BV41" s="2"/>
       <c r="BW41" s="2" t="s">
         <v>450</v>
       </c>
       <c r="BX41" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="BY41" s="2" t="s">
         <v>514</v>
@@ -10232,66 +10228,66 @@
       <c r="BZ41" s="2"/>
       <c r="CA41" s="2"/>
       <c r="CB41" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="CC41" s="2"/>
       <c r="CD41" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="CE41" s="2"/>
       <c r="CF41" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="CG41" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="CG41" s="2" t="s">
+      <c r="CH41" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="CH41" s="2" t="s">
+      <c r="CI41" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="CJ41" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="CK41" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="CL41" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="CI41" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="CJ41" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="CK41" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="CL41" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="CM41" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="CN41" s="2" t="s">
         <v>173</v>
       </c>
       <c r="CO41" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="CP41" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="CP41" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="CQ41" s="2" t="s">
         <v>550</v>
       </c>
       <c r="CR41" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="CS41" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="CT41" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="CS41" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="CT41" s="2" t="s">
+      <c r="CU41" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="CU41" s="2" t="s">
+      <c r="CV41" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="CV41" s="3" t="s">
-        <v>608</v>
-      </c>
     </row>
-    <row r="42" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>326</v>
       </c>
@@ -10314,10 +10310,10 @@
         <v>279</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -10374,14 +10370,14 @@
       <c r="BJ42" s="2"/>
       <c r="BK42" s="2"/>
       <c r="BL42" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="BM42" s="2"/>
       <c r="BN42" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="BO42" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="BP42" s="2">
         <v>1</v>
@@ -10391,22 +10387,22 @@
       </c>
       <c r="BR42" s="2"/>
       <c r="BS42" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="BT42" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="BT42" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="BU42" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV42" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="BW42" s="2" t="s">
         <v>450</v>
       </c>
       <c r="BX42" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="BY42" s="2" t="s">
         <v>514</v>
@@ -10418,62 +10414,62 @@
       </c>
       <c r="CC42" s="2"/>
       <c r="CD42" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="CE42" s="2"/>
       <c r="CF42" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="CG42" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="CG42" s="2" t="s">
+      <c r="CH42" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="CH42" s="2" t="s">
+      <c r="CI42" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="CI42" s="2" t="s">
+      <c r="CJ42" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="CJ42" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="CK42" s="2" t="s">
         <v>110</v>
       </c>
       <c r="CL42" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="CM42" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="CN42" s="2" t="s">
         <v>328</v>
       </c>
       <c r="CO42" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="CP42" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="CP42" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="CQ42" s="2" t="s">
         <v>550</v>
       </c>
       <c r="CR42" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="CS42" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="CS42" s="2" t="s">
+      <c r="CT42" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="CU42" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="CT42" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="CU42" s="2" t="s">
+      <c r="CV42" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="CV42" s="2" t="s">
-        <v>628</v>
-      </c>
     </row>
-    <row r="43" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>421</v>
       </c>
@@ -10496,7 +10492,7 @@
         <v>425</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>503</v>
@@ -10556,14 +10552,14 @@
       <c r="BJ43" s="2"/>
       <c r="BK43" s="2"/>
       <c r="BL43" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="BM43" s="2"/>
       <c r="BN43" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="BO43" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="BP43" s="2">
         <v>1</v>
@@ -10573,22 +10569,22 @@
       </c>
       <c r="BR43" s="2"/>
       <c r="BS43" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="BT43" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="BT43" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="BU43" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV43" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="BW43" s="2" t="s">
         <v>450</v>
       </c>
       <c r="BX43" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="BY43" s="2" t="s">
         <v>514</v>
@@ -10596,36 +10592,36 @@
       <c r="BZ43" s="2"/>
       <c r="CA43" s="2"/>
       <c r="CB43" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="CC43" s="2"/>
       <c r="CD43" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="CE43" s="2"/>
       <c r="CF43" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="CG43" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="CG43" s="2" t="s">
+      <c r="CH43" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="CH43" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="CI43" s="2" t="s">
         <v>450</v>
       </c>
       <c r="CJ43" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="CK43" s="2" t="s">
         <v>110</v>
       </c>
       <c r="CL43" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="CM43" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="CN43" s="2" t="s">
         <v>423</v>
@@ -10640,10 +10636,10 @@
         <v>550</v>
       </c>
       <c r="CR43" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="CS43" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="CS43" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="CT43" s="2" t="s">
         <v>553</v>
@@ -10651,7 +10647,7 @@
       <c r="CU43" s="2"/>
       <c r="CV43" s="2"/>
     </row>
-    <row r="44" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>137</v>
       </c>
@@ -10674,10 +10670,10 @@
         <v>142</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -10734,114 +10730,114 @@
       <c r="BJ44" s="2"/>
       <c r="BK44" s="2"/>
       <c r="BL44" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="BM44" s="2"/>
       <c r="BN44" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="BO44" s="2" t="s">
         <v>505</v>
       </c>
       <c r="BP44" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="BQ44" s="2" t="s">
         <v>532</v>
       </c>
       <c r="BR44" s="2"/>
       <c r="BS44" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="BT44" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="BT44" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="BU44" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV44" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="BW44" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="BW44" s="2" t="s">
+      <c r="BX44" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="BX44" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="BY44" s="2" t="s">
         <v>537</v>
       </c>
       <c r="BZ44" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="CA44" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="CB44" s="2" t="s">
         <v>80</v>
       </c>
       <c r="CC44" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="CD44" s="2" t="s">
         <v>82</v>
       </c>
       <c r="CE44" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="CF44" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="CG44" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="CH44" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="CF44" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="CG44" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="CH44" s="2" t="s">
+      <c r="CI44" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="CI44" s="2" t="s">
+      <c r="CJ44" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="CJ44" s="2" t="s">
+      <c r="CK44" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="CK44" s="2" t="s">
+      <c r="CL44" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="CL44" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="CM44" s="2" t="s">
         <v>524</v>
       </c>
       <c r="CN44" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="CO44" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="CO44" s="2" t="s">
+      <c r="CP44" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="CP44" s="2" t="s">
+      <c r="CQ44" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="CR44" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="CQ44" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="CR44" s="2" t="s">
+      <c r="CS44" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="CS44" s="2" t="s">
+      <c r="CT44" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="CU44" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="CT44" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="CU44" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="CV44" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
-    <row r="45" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>137</v>
       </c>
@@ -10864,10 +10860,10 @@
         <v>142</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -10928,37 +10924,37 @@
       </c>
       <c r="BM45" s="2"/>
       <c r="BN45" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="BO45" s="2" t="s">
         <v>505</v>
       </c>
       <c r="BP45" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="BQ45" s="2" t="s">
         <v>506</v>
       </c>
       <c r="BR45" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="BS45" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="BS45" s="2" t="s">
+      <c r="BT45" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="BT45" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="BU45" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV45" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="BW45" s="2" t="s">
         <v>450</v>
       </c>
       <c r="BX45" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="BY45" s="2" t="s">
         <v>514</v>
@@ -10973,49 +10969,49 @@
         <v>82</v>
       </c>
       <c r="CE45" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="CF45" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="CF45" s="2" t="s">
+      <c r="CG45" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="CG45" s="2" t="s">
+      <c r="CH45" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="CH45" s="2" t="s">
+      <c r="CI45" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="CI45" s="2" t="s">
+      <c r="CJ45" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="CJ45" s="2" t="s">
-        <v>676</v>
-      </c>
       <c r="CK45" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="CL45" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="CM45" s="2" t="s">
         <v>524</v>
       </c>
       <c r="CN45" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="CO45" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="CO45" s="2" t="s">
+      <c r="CP45" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="CQ45" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="CR45" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="CP45" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="CQ45" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="CR45" s="2" t="s">
+      <c r="CS45" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="CS45" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="CT45" s="2" t="s">
         <v>553</v>
@@ -11023,7 +11019,7 @@
       <c r="CU45" s="2"/>
       <c r="CV45" s="2"/>
     </row>
-    <row r="46" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>137</v>
       </c>
@@ -11046,10 +11042,10 @@
         <v>142</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -11110,44 +11106,44 @@
       </c>
       <c r="BM46" s="2"/>
       <c r="BN46" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="BO46" s="2" t="s">
         <v>505</v>
       </c>
       <c r="BP46" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="BQ46" s="2" t="s">
         <v>532</v>
       </c>
       <c r="BR46" s="2"/>
       <c r="BS46" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="BT46" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="BT46" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="BU46" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV46" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="BW46" s="2" t="s">
         <v>450</v>
       </c>
       <c r="BX46" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="BY46" s="2" t="s">
         <v>537</v>
       </c>
       <c r="BZ46" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="CA46" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="CA46" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="CB46" s="2" t="s">
         <v>515</v>
@@ -11160,43 +11156,43 @@
         <v>442</v>
       </c>
       <c r="CF46" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="CG46" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="CG46" s="2" t="s">
+      <c r="CH46" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="CH46" s="2" t="s">
+      <c r="CI46" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="CI46" s="2" t="s">
+      <c r="CJ46" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="CJ46" s="2" t="s">
-        <v>692</v>
-      </c>
       <c r="CK46" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="CL46" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="CL46" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="CM46" s="2" t="s">
         <v>524</v>
       </c>
       <c r="CN46" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="CO46" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="CP46" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="CQ46" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="CR46" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="CO46" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="CP46" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="CQ46" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="CR46" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="CS46" s="2" t="s">
         <v>413</v>
@@ -11207,7 +11203,7 @@
       <c r="CU46" s="2"/>
       <c r="CV46" s="2"/>
     </row>
-    <row r="47" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>137</v>
       </c>
@@ -11230,7 +11226,7 @@
         <v>142</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>528</v>
@@ -11294,43 +11290,43 @@
       </c>
       <c r="BM47" s="2"/>
       <c r="BN47" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="BO47" s="2" t="s">
         <v>505</v>
       </c>
       <c r="BP47" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="BQ47" s="2" t="s">
         <v>506</v>
       </c>
       <c r="BR47" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="BS47" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="BS47" s="2" t="s">
+      <c r="BT47" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="BT47" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="BU47" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV47" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="BW47" s="2" t="s">
         <v>450</v>
       </c>
       <c r="BX47" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="BY47" s="2" t="s">
         <v>537</v>
       </c>
       <c r="BZ47" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="CA47" s="2" t="s">
         <v>413</v>
@@ -11343,28 +11339,28 @@
         <v>82</v>
       </c>
       <c r="CE47" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="CF47" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="CG47" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="CH47" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="CH47" s="2" t="s">
+      <c r="CI47" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="CJ47" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="CI47" s="2" t="s">
+      <c r="CK47" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="CL47" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="CJ47" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="CK47" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="CL47" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="CM47" s="2" t="s">
         <v>524</v>
@@ -11373,16 +11369,16 @@
         <v>413</v>
       </c>
       <c r="CO47" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="CP47" s="2" t="s">
         <v>413</v>
       </c>
       <c r="CQ47" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="CR47" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="CS47" s="2" t="s">
         <v>413</v>
@@ -11393,7 +11389,7 @@
       <c r="CU47" s="2"/>
       <c r="CV47" s="2"/>
     </row>
-    <row r="48" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>454</v>
       </c>
@@ -11416,7 +11412,7 @@
         <v>460</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>528</v>
@@ -11476,11 +11472,11 @@
       <c r="BJ48" s="2"/>
       <c r="BK48" s="2"/>
       <c r="BL48" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="BM48" s="2"/>
       <c r="BN48" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="BO48" s="2" t="s">
         <v>530</v>
@@ -11493,22 +11489,22 @@
       </c>
       <c r="BR48" s="2"/>
       <c r="BS48" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="BT48" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="BT48" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="BU48" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV48" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="BW48" s="2" t="s">
         <v>464</v>
       </c>
       <c r="BX48" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="BY48" s="2" t="s">
         <v>514</v>
@@ -11523,16 +11519,16 @@
         <v>82</v>
       </c>
       <c r="CE48" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="CF48" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="CF48" s="2" t="s">
-        <v>711</v>
-      </c>
       <c r="CG48" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="CH48" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="CI48" s="2" t="s">
         <v>110</v>
@@ -11544,7 +11540,7 @@
         <v>110</v>
       </c>
       <c r="CL48" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="CM48" s="2" t="s">
         <v>524</v>
@@ -11559,13 +11555,13 @@
         <v>464</v>
       </c>
       <c r="CQ48" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="CR48" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="CR48" s="2" t="s">
-        <v>714</v>
-      </c>
       <c r="CS48" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="CT48" s="2" t="s">
         <v>553</v>
@@ -11599,7 +11595,7 @@
         <v>189</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -11695,7 +11691,7 @@
       <c r="CU49" s="2"/>
       <c r="CV49" s="2"/>
     </row>
-    <row r="50" spans="1:100" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>484</v>
       </c>
@@ -11718,7 +11714,7 @@
         <v>106</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>528</v>
@@ -11782,35 +11778,35 @@
       </c>
       <c r="BM50" s="2"/>
       <c r="BN50" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="BO50" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="BP50" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="BO50" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="BP50" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="BQ50" s="2" t="s">
         <v>532</v>
       </c>
       <c r="BR50" s="2"/>
       <c r="BS50" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="BT50" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="BT50" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="BU50" s="2" t="s">
         <v>510</v>
       </c>
       <c r="BV50" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="BW50" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="BX50" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="BW50" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="BX50" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="BY50" s="2" t="s">
         <v>514</v>
@@ -11825,49 +11821,49 @@
         <v>82</v>
       </c>
       <c r="CE50" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="CF50" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="CF50" s="2" t="s">
+      <c r="CG50" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="CG50" s="2" t="s">
+      <c r="CH50" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="CH50" s="2" t="s">
+      <c r="CI50" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="CI50" s="2" t="s">
+      <c r="CJ50" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="CJ50" s="2" t="s">
+      <c r="CK50" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="CK50" s="2" t="s">
-        <v>728</v>
-      </c>
       <c r="CL50" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="CM50" s="2" t="s">
         <v>524</v>
       </c>
       <c r="CN50" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="CO50" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="CO50" s="2" t="s">
+      <c r="CP50" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="CP50" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="CQ50" s="2" t="s">
         <v>550</v>
       </c>
       <c r="CR50" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="CS50" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="CT50" s="2" t="s">
         <v>553</v>
@@ -11877,14 +11873,14 @@
     </row>
     <row r="51" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>269</v>
@@ -11897,7 +11893,7 @@
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -11993,10 +11989,10 @@
     </row>
     <row r="52" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>735</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>736</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
@@ -12013,7 +12009,7 @@
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -12109,7 +12105,7 @@
     </row>
     <row r="53" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>499</v>
@@ -12129,7 +12125,7 @@
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -12225,27 +12221,27 @@
     </row>
     <row r="54" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>738</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>739</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>195</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -12341,14 +12337,14 @@
     </row>
     <row r="55" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>742</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>104</v>
@@ -12361,7 +12357,7 @@
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -12457,17 +12453,17 @@
     </row>
     <row r="56" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>743</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>744</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>187</v>
@@ -12477,7 +12473,7 @@
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -12573,17 +12569,17 @@
     </row>
     <row r="57" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>745</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>746</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
         <v>424</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>459</v>
@@ -12593,7 +12589,7 @@
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -12689,10 +12685,10 @@
     </row>
     <row r="58" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>747</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>748</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
@@ -12705,11 +12701,11 @@
         <v>164</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -12805,10 +12801,10 @@
     </row>
     <row r="59" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>749</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>750</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
@@ -12821,11 +12817,11 @@
         <v>141</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -12921,14 +12917,14 @@
     </row>
     <row r="60" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>752</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>753</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>104</v>
@@ -12941,7 +12937,7 @@
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -13037,10 +13033,10 @@
     </row>
     <row r="61" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
@@ -13057,7 +13053,7 @@
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -13153,10 +13149,10 @@
     </row>
     <row r="62" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
@@ -13173,7 +13169,7 @@
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -13269,14 +13265,14 @@
     </row>
     <row r="63" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>104</v>
@@ -13289,7 +13285,7 @@
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -13385,10 +13381,10 @@
     </row>
     <row r="64" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>761</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
@@ -13405,7 +13401,7 @@
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -13501,27 +13497,27 @@
     </row>
     <row r="65" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>738</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>739</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>195</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
@@ -13617,10 +13613,10 @@
     </row>
     <row r="66" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
@@ -13637,7 +13633,7 @@
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -13733,10 +13729,10 @@
     </row>
     <row r="67" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
@@ -13753,7 +13749,7 @@
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -13849,27 +13845,27 @@
     </row>
     <row r="68" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>795</v>
-      </c>
       <c r="G68" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
@@ -13965,14 +13961,14 @@
     </row>
     <row r="69" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>269</v>
@@ -13981,11 +13977,11 @@
         <v>187</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
@@ -14081,14 +14077,14 @@
     </row>
     <row r="70" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>269</v>
@@ -14097,11 +14093,11 @@
         <v>187</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -14197,27 +14193,27 @@
     </row>
     <row r="71" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E71" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>795</v>
-      </c>
       <c r="G71" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -14313,10 +14309,10 @@
     </row>
     <row r="72" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
@@ -14333,7 +14329,7 @@
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -14429,10 +14425,10 @@
     </row>
     <row r="73" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
@@ -14449,7 +14445,7 @@
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -14545,10 +14541,10 @@
     </row>
     <row r="74" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
@@ -14565,7 +14561,7 @@
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -14661,7 +14657,7 @@
     </row>
     <row r="75" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>499</v>
@@ -14681,7 +14677,7 @@
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
@@ -14777,10 +14773,10 @@
     </row>
     <row r="76" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
@@ -14797,7 +14793,7 @@
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
@@ -14893,14 +14889,14 @@
     </row>
     <row r="77" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>783</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>784</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>104</v>
@@ -14909,11 +14905,11 @@
         <v>164</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
@@ -15009,10 +15005,10 @@
     </row>
     <row r="78" spans="1:100" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
@@ -15029,7 +15025,7 @@
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
@@ -15124,13 +15120,7 @@
       <c r="CV78" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CV78" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters blank="1">
-        <filter val="NATURE_NON_RENSEIGNEE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:CV78" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="C38" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>

--- a/Data/Questionnaires/Questionnaires_SLAM_B.xlsx
+++ b/Data/Questionnaires/Questionnaires_SLAM_B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\Questionnaires\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D61C90F-18D2-4A62-8FB1-1A51BC5CF0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9C4433-3DF1-472B-837A-C1640F1A3556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questionnaires_SLAM_B" sheetId="1" r:id="rId1"/>
@@ -4070,7 +4070,7 @@
       <c r="CW2" s="3"/>
       <c r="CX2" s="3"/>
     </row>
-    <row r="3" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>782</v>
       </c>
@@ -5276,7 +5276,7 @@
       <c r="CW9" s="3"/>
       <c r="CX9" s="3"/>
     </row>
-    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>782</v>
       </c>
@@ -5936,7 +5936,7 @@
       <c r="CW13" s="3"/>
       <c r="CX13" s="3"/>
     </row>
-    <row r="14" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>782</v>
       </c>
@@ -5989,7 +5989,7 @@
       <c r="R14" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="6" t="s">
         <v>278</v>
       </c>
       <c r="T14" s="3" t="s">
@@ -6452,7 +6452,7 @@
       <c r="CW16" s="3"/>
       <c r="CX16" s="3"/>
     </row>
-    <row r="17" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>782</v>
       </c>
@@ -8112,7 +8112,7 @@
       <c r="CW25" s="3"/>
       <c r="CX25" s="3"/>
     </row>
-    <row r="26" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>782</v>
       </c>
@@ -8314,7 +8314,7 @@
       <c r="CW26" s="3"/>
       <c r="CX26" s="3"/>
     </row>
-    <row r="27" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>782</v>
       </c>
@@ -8652,7 +8652,7 @@
       <c r="CW28" s="3"/>
       <c r="CX28" s="3"/>
     </row>
-    <row r="29" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>782</v>
       </c>
@@ -8834,7 +8834,7 @@
       <c r="CW29" s="3"/>
       <c r="CX29" s="3"/>
     </row>
-    <row r="30" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>782</v>
       </c>
@@ -9206,7 +9206,7 @@
       <c r="CW31" s="3"/>
       <c r="CX31" s="3"/>
     </row>
-    <row r="32" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>782</v>
       </c>
@@ -10632,7 +10632,7 @@
       <c r="CW39" s="3"/>
       <c r="CX39" s="3"/>
     </row>
-    <row r="40" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>783</v>
       </c>
@@ -11008,7 +11008,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="42" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>783</v>
       </c>
@@ -12146,7 +12146,7 @@
       <c r="CW47" s="3"/>
       <c r="CX47" s="3"/>
     </row>
-    <row r="48" spans="1:102" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>783</v>
       </c>
@@ -16316,14 +16316,25 @@
     </filterColumn>
     <filterColumn colId="7">
       <filters>
-        <filter val="3"/>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="1.4b"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="PRODUITES"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="D38" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S14" r:id="rId2" xr:uid="{6EAA74DF-1F24-4AAC-B3D4-3D02BD34995E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="8" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Data/Questionnaires/Questionnaires_SLAM_B.xlsx
+++ b/Data/Questionnaires/Questionnaires_SLAM_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\Questionnaires\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9C4433-3DF1-472B-837A-C1640F1A3556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345533FE-A4F5-4C4E-BCDC-F1973C6CDC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3479,7 +3479,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:CX79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3886,7 +3885,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>782</v>
       </c>
@@ -4256,7 +4255,7 @@
       <c r="CW3" s="3"/>
       <c r="CX3" s="3"/>
     </row>
-    <row r="4" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>782</v>
       </c>
@@ -4442,7 +4441,7 @@
       <c r="CW4" s="3"/>
       <c r="CX4" s="3"/>
     </row>
-    <row r="5" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>784</v>
       </c>
@@ -4578,7 +4577,7 @@
       <c r="CW5" s="3"/>
       <c r="CX5" s="3"/>
     </row>
-    <row r="6" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>782</v>
       </c>
@@ -4770,7 +4769,7 @@
       <c r="CW6" s="3"/>
       <c r="CX6" s="3"/>
     </row>
-    <row r="7" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>782</v>
       </c>
@@ -4954,7 +4953,7 @@
       <c r="CW7" s="3"/>
       <c r="CX7" s="3"/>
     </row>
-    <row r="8" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>782</v>
       </c>
@@ -5140,7 +5139,7 @@
       <c r="CW8" s="3"/>
       <c r="CX8" s="3"/>
     </row>
-    <row r="9" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>784</v>
       </c>
@@ -5276,7 +5275,7 @@
       <c r="CW9" s="3"/>
       <c r="CX9" s="3"/>
     </row>
-    <row r="10" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>782</v>
       </c>
@@ -5466,7 +5465,7 @@
       <c r="CW10" s="3"/>
       <c r="CX10" s="3"/>
     </row>
-    <row r="11" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>782</v>
       </c>
@@ -5632,7 +5631,7 @@
       <c r="CW11" s="3"/>
       <c r="CX11" s="3"/>
     </row>
-    <row r="12" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>782</v>
       </c>
@@ -5798,7 +5797,7 @@
       <c r="CW12" s="3"/>
       <c r="CX12" s="3"/>
     </row>
-    <row r="13" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>784</v>
       </c>
@@ -5936,7 +5935,7 @@
       <c r="CW13" s="3"/>
       <c r="CX13" s="3"/>
     </row>
-    <row r="14" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>782</v>
       </c>
@@ -6126,7 +6125,7 @@
       <c r="CW14" s="3"/>
       <c r="CX14" s="3"/>
     </row>
-    <row r="15" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>782</v>
       </c>
@@ -6314,7 +6313,7 @@
       <c r="CW15" s="3"/>
       <c r="CX15" s="3"/>
     </row>
-    <row r="16" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>784</v>
       </c>
@@ -6452,7 +6451,7 @@
       <c r="CW16" s="3"/>
       <c r="CX16" s="3"/>
     </row>
-    <row r="17" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>782</v>
       </c>
@@ -6636,7 +6635,7 @@
       <c r="CW17" s="3"/>
       <c r="CX17" s="3"/>
     </row>
-    <row r="18" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>782</v>
       </c>
@@ -6816,7 +6815,7 @@
       <c r="CW18" s="3"/>
       <c r="CX18" s="3"/>
     </row>
-    <row r="19" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>782</v>
       </c>
@@ -6998,7 +6997,7 @@
       <c r="CW19" s="3"/>
       <c r="CX19" s="3"/>
     </row>
-    <row r="20" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>782</v>
       </c>
@@ -7188,7 +7187,7 @@
       <c r="CW20" s="3"/>
       <c r="CX20" s="3"/>
     </row>
-    <row r="21" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>782</v>
       </c>
@@ -7380,7 +7379,7 @@
       <c r="CW21" s="3"/>
       <c r="CX21" s="3"/>
     </row>
-    <row r="22" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>782</v>
       </c>
@@ -7558,7 +7557,7 @@
       <c r="CW22" s="3"/>
       <c r="CX22" s="3"/>
     </row>
-    <row r="23" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>782</v>
       </c>
@@ -7740,7 +7739,7 @@
       <c r="CW23" s="3"/>
       <c r="CX23" s="3"/>
     </row>
-    <row r="24" spans="1:102" ht="87" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:102" ht="87" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>782</v>
       </c>
@@ -7922,7 +7921,7 @@
       <c r="CW24" s="3"/>
       <c r="CX24" s="3"/>
     </row>
-    <row r="25" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>782</v>
       </c>
@@ -8516,7 +8515,7 @@
       <c r="CW27" s="3"/>
       <c r="CX27" s="3"/>
     </row>
-    <row r="28" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>784</v>
       </c>
@@ -8652,7 +8651,7 @@
       <c r="CW28" s="3"/>
       <c r="CX28" s="3"/>
     </row>
-    <row r="29" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>782</v>
       </c>
@@ -9022,7 +9021,7 @@
       <c r="CW30" s="3"/>
       <c r="CX30" s="3"/>
     </row>
-    <row r="31" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>782</v>
       </c>
@@ -9206,7 +9205,7 @@
       <c r="CW31" s="3"/>
       <c r="CX31" s="3"/>
     </row>
-    <row r="32" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>782</v>
       </c>
@@ -9382,7 +9381,7 @@
       <c r="CW32" s="3"/>
       <c r="CX32" s="3"/>
     </row>
-    <row r="33" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>782</v>
       </c>
@@ -9580,7 +9579,7 @@
       <c r="CW33" s="3"/>
       <c r="CX33" s="3"/>
     </row>
-    <row r="34" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>784</v>
       </c>
@@ -9716,7 +9715,7 @@
       <c r="CW34" s="3"/>
       <c r="CX34" s="3"/>
     </row>
-    <row r="35" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>782</v>
       </c>
@@ -9900,7 +9899,7 @@
       <c r="CW35" s="3"/>
       <c r="CX35" s="3"/>
     </row>
-    <row r="36" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>782</v>
       </c>
@@ -10064,7 +10063,7 @@
       <c r="CW36" s="3"/>
       <c r="CX36" s="3"/>
     </row>
-    <row r="37" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>782</v>
       </c>
@@ -10252,7 +10251,7 @@
       <c r="CW37" s="3"/>
       <c r="CX37" s="3"/>
     </row>
-    <row r="38" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>783</v>
       </c>
@@ -10444,7 +10443,7 @@
       <c r="CW38" s="3"/>
       <c r="CX38" s="3"/>
     </row>
-    <row r="39" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>783</v>
       </c>
@@ -10632,7 +10631,7 @@
       <c r="CW39" s="3"/>
       <c r="CX39" s="3"/>
     </row>
-    <row r="40" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>783</v>
       </c>
@@ -10818,7 +10817,7 @@
       <c r="CW40" s="3"/>
       <c r="CX40" s="3"/>
     </row>
-    <row r="41" spans="1:102" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:102" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>783</v>
       </c>
@@ -11008,7 +11007,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="42" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>783</v>
       </c>
@@ -11196,7 +11195,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="43" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>783</v>
       </c>
@@ -11380,7 +11379,7 @@
       <c r="CW43" s="3"/>
       <c r="CX43" s="3"/>
     </row>
-    <row r="44" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>783</v>
       </c>
@@ -11576,7 +11575,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="45" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>783</v>
       </c>
@@ -11764,7 +11763,7 @@
       <c r="CW45" s="3"/>
       <c r="CX45" s="3"/>
     </row>
-    <row r="46" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>783</v>
       </c>
@@ -11954,7 +11953,7 @@
       <c r="CW46" s="3"/>
       <c r="CX46" s="3"/>
     </row>
-    <row r="47" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>783</v>
       </c>
@@ -12146,7 +12145,7 @@
       <c r="CW47" s="3"/>
       <c r="CX47" s="3"/>
     </row>
-    <row r="48" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>783</v>
       </c>
@@ -12332,7 +12331,7 @@
       <c r="CW48" s="3"/>
       <c r="CX48" s="3"/>
     </row>
-    <row r="49" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>784</v>
       </c>
@@ -12460,7 +12459,7 @@
       <c r="CW49" s="3"/>
       <c r="CX49" s="3"/>
     </row>
-    <row r="50" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>783</v>
       </c>
@@ -12646,7 +12645,7 @@
       <c r="CW50" s="3"/>
       <c r="CX50" s="3"/>
     </row>
-    <row r="51" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>783</v>
       </c>
@@ -12834,7 +12833,7 @@
       <c r="CW51" s="3"/>
       <c r="CX51" s="3"/>
     </row>
-    <row r="52" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>784</v>
       </c>
@@ -12958,7 +12957,7 @@
       <c r="CW52" s="3"/>
       <c r="CX52" s="3"/>
     </row>
-    <row r="53" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>784</v>
       </c>
@@ -13082,7 +13081,7 @@
       <c r="CW53" s="3"/>
       <c r="CX53" s="3"/>
     </row>
-    <row r="54" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>784</v>
       </c>
@@ -13206,7 +13205,7 @@
       <c r="CW54" s="3"/>
       <c r="CX54" s="3"/>
     </row>
-    <row r="55" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>784</v>
       </c>
@@ -13330,7 +13329,7 @@
       <c r="CW55" s="3"/>
       <c r="CX55" s="3"/>
     </row>
-    <row r="56" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>784</v>
       </c>
@@ -13454,7 +13453,7 @@
       <c r="CW56" s="3"/>
       <c r="CX56" s="3"/>
     </row>
-    <row r="57" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>784</v>
       </c>
@@ -13578,7 +13577,7 @@
       <c r="CW57" s="3"/>
       <c r="CX57" s="3"/>
     </row>
-    <row r="58" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>784</v>
       </c>
@@ -13702,7 +13701,7 @@
       <c r="CW58" s="3"/>
       <c r="CX58" s="3"/>
     </row>
-    <row r="59" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>784</v>
       </c>
@@ -13826,7 +13825,7 @@
       <c r="CW59" s="3"/>
       <c r="CX59" s="3"/>
     </row>
-    <row r="60" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>784</v>
       </c>
@@ -13950,7 +13949,7 @@
       <c r="CW60" s="3"/>
       <c r="CX60" s="3"/>
     </row>
-    <row r="61" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>784</v>
       </c>
@@ -14074,7 +14073,7 @@
       <c r="CW61" s="3"/>
       <c r="CX61" s="3"/>
     </row>
-    <row r="62" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>784</v>
       </c>
@@ -14198,7 +14197,7 @@
       <c r="CW62" s="3"/>
       <c r="CX62" s="3"/>
     </row>
-    <row r="63" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>784</v>
       </c>
@@ -14322,7 +14321,7 @@
       <c r="CW63" s="3"/>
       <c r="CX63" s="3"/>
     </row>
-    <row r="64" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>784</v>
       </c>
@@ -14446,7 +14445,7 @@
       <c r="CW64" s="3"/>
       <c r="CX64" s="3"/>
     </row>
-    <row r="65" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>784</v>
       </c>
@@ -14570,7 +14569,7 @@
       <c r="CW65" s="3"/>
       <c r="CX65" s="3"/>
     </row>
-    <row r="66" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>784</v>
       </c>
@@ -14694,7 +14693,7 @@
       <c r="CW66" s="3"/>
       <c r="CX66" s="3"/>
     </row>
-    <row r="67" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>784</v>
       </c>
@@ -14818,7 +14817,7 @@
       <c r="CW67" s="3"/>
       <c r="CX67" s="3"/>
     </row>
-    <row r="68" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>784</v>
       </c>
@@ -14942,7 +14941,7 @@
       <c r="CW68" s="3"/>
       <c r="CX68" s="3"/>
     </row>
-    <row r="69" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>784</v>
       </c>
@@ -15066,7 +15065,7 @@
       <c r="CW69" s="3"/>
       <c r="CX69" s="3"/>
     </row>
-    <row r="70" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>784</v>
       </c>
@@ -15190,7 +15189,7 @@
       <c r="CW70" s="3"/>
       <c r="CX70" s="3"/>
     </row>
-    <row r="71" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>784</v>
       </c>
@@ -15314,7 +15313,7 @@
       <c r="CW71" s="3"/>
       <c r="CX71" s="3"/>
     </row>
-    <row r="72" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>784</v>
       </c>
@@ -15438,7 +15437,7 @@
       <c r="CW72" s="3"/>
       <c r="CX72" s="3"/>
     </row>
-    <row r="73" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>784</v>
       </c>
@@ -15562,7 +15561,7 @@
       <c r="CW73" s="3"/>
       <c r="CX73" s="3"/>
     </row>
-    <row r="74" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>784</v>
       </c>
@@ -15686,7 +15685,7 @@
       <c r="CW74" s="3"/>
       <c r="CX74" s="3"/>
     </row>
-    <row r="75" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>784</v>
       </c>
@@ -15810,7 +15809,7 @@
       <c r="CW75" s="3"/>
       <c r="CX75" s="3"/>
     </row>
-    <row r="76" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>784</v>
       </c>
@@ -15934,7 +15933,7 @@
       <c r="CW76" s="3"/>
       <c r="CX76" s="3"/>
     </row>
-    <row r="77" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>784</v>
       </c>
@@ -16058,7 +16057,7 @@
       <c r="CW77" s="3"/>
       <c r="CX77" s="3"/>
     </row>
-    <row r="78" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>784</v>
       </c>
@@ -16182,7 +16181,7 @@
       <c r="CW78" s="3"/>
       <c r="CX78" s="3"/>
     </row>
-    <row r="79" spans="1:102" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>784</v>
       </c>
@@ -16307,29 +16306,7 @@
       <c r="CX79" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CX79" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="CODES"/>
-        <filter val="DATA"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters>
-        <filter val="1.4b"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="10">
-      <filters>
-        <filter val="PRODUITES"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:CX79" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="D38" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="S14" r:id="rId2" xr:uid="{6EAA74DF-1F24-4AAC-B3D4-3D02BD34995E}"/>
